--- a/tables/datas/common/#Ai-AI配置表.xlsx
+++ b/tables/datas/common/#Ai-AI配置表.xlsx
@@ -124,6 +124,45 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>System</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>AI 行为模式
+patrol = 巡逻
+patrol_chase = 巡逻+追击
+guard = 守卫（原地不动）</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>仇恨范围（格子数）
+0 = 无仇恨</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>巡逻范围（格子数）
+0 = 不巡逻</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>战斗行为类型（common.ECombatBehaviorType 枚举）
+Auto = 自动推断（根据技能射程）
+Melee = 近战追击
+Ranged = 远程攻击
+Caster = 施法者</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -413,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,40 +473,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>aggro_range</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>move_interval_ms</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>chase_interval_ms</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>max_chase_distance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>patrol_range</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>param_1</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>param_2</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>param_3</t>
         </is>
@@ -491,40 +535,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>common.ECombatBehaviorType</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -548,40 +597,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>AI行为描述</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>警戒半径</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>巡逻间隔毫秒</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>追击间隔毫秒</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>最大追击距离</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>巡逻范围</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>扩展参数1</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>战斗行为类型</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>扩展参数2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>扩展参数3</t>
         </is>
@@ -605,40 +659,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -653,28 +712,35 @@
           <t>patrol</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>patrol sample</t>
+        </is>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>1500</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -687,28 +753,35 @@
           <t>patrol_chase</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>melee sample</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>2000</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>500</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -721,32 +794,122 @@
           <t>guard</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>guard sample</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>300</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>patrol_chase</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ranged sample</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>500</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>guard</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>caster sample</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Caster</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/tables/datas/common/#Ai-AI配置表.xlsx
+++ b/tables/datas/common/#Ai-AI配置表.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,6 +516,26 @@
           <t>param_3</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>territory_radius</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>chase_timeout</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>return_buff_id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>return_speed_multiplier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -578,6 +598,26 @@
           <t>float</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -640,6 +680,26 @@
           <t>扩展参数3</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>领地范围半径（格数）</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>追击超时时间（秒）</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>回归Buff ID</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>回归移速倍率</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -700,6 +760,26 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>s</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>cs</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>cs</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
@@ -743,6 +823,18 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -784,6 +876,18 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -825,6 +929,18 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -866,6 +982,18 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -906,6 +1034,18 @@
       </c>
       <c r="L9" t="n">
         <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
